--- a/backups/tickets-backup-2026-04-07.xlsx
+++ b/backups/tickets-backup-2026-04-07.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="94">
   <si>
     <t>ID</t>
   </si>
@@ -44,9 +44,6 @@
   </si>
   <si>
     <t>Time Since (days)</t>
-  </si>
-  <si>
-    <t>Created At</t>
   </si>
   <si>
     <t>CRM 2025 Renewals Dashboard</t>
@@ -695,22 +692,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="40" customWidth="1"/>
-    <col min="3" max="5" width="20" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="50" customWidth="1"/>
-    <col min="8" max="8" width="22" customWidth="1"/>
-    <col min="9" max="9" width="16" customWidth="1"/>
-    <col min="10" max="10" width="22" customWidth="1"/>
-    <col min="11" max="11" width="20" customWidth="1"/>
-    <col min="12" max="12" width="22" customWidth="1"/>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="71" customWidth="1"/>
+    <col min="3" max="3" width="21" customWidth="1"/>
+    <col min="4" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="62" customWidth="1"/>
+    <col min="8" max="8" width="18" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="18" customWidth="1"/>
+    <col min="11" max="11" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="22" customHeight="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -744,771 +741,709 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="D2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="I2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>20</v>
       </c>
       <c r="K2" s="2">
         <v>12</v>
       </c>
-      <c r="L2" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>27</v>
-      </c>
       <c r="I3" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K3" s="3">
         <v>12</v>
       </c>
-      <c r="L3" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>31</v>
       </c>
       <c r="K4" s="2">
         <v>12</v>
       </c>
-      <c r="L4" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>6</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" s="3" t="s">
+      <c r="H5" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="3" t="s">
-        <v>35</v>
-      </c>
       <c r="I5" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K5" s="3">
         <v>12</v>
       </c>
-      <c r="L5" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>7</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="H6" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="I6" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K6" s="2">
         <v>7</v>
       </c>
-      <c r="L6" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>8</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="3" t="s">
+      <c r="F7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="G7" s="3" t="s">
+      <c r="H7" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="H7" s="3" t="s">
-        <v>44</v>
-      </c>
       <c r="I7" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K7" s="3">
         <v>7</v>
       </c>
-      <c r="L7" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>9</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>48</v>
-      </c>
       <c r="I8" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K8" s="2">
         <v>7</v>
       </c>
-      <c r="L8" s="2" t="s">
+    </row>
+    <row r="9" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3">
+        <v>13</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3">
-        <v>13</v>
-      </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="G9" s="3" t="s">
+      <c r="H9" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>52</v>
-      </c>
       <c r="I9" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K9" s="3">
         <v>7</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>14</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H10" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="H10" s="2" t="s">
+      <c r="I10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J10" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>56</v>
       </c>
       <c r="K10" s="2">
         <v>7</v>
       </c>
-      <c r="L10" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>11</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G11" s="3" t="s">
+      <c r="H11" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="H11" s="3" t="s">
-        <v>60</v>
-      </c>
       <c r="I11" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K11" s="3">
         <v>7</v>
       </c>
-      <c r="L11" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>10</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G12" s="2" t="s">
+      <c r="H12" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="H12" s="2" t="s">
-        <v>63</v>
-      </c>
       <c r="I12" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K12" s="2">
         <v>7</v>
       </c>
-      <c r="L12" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>16</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="H13" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>66</v>
-      </c>
       <c r="I13" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K13" s="3">
         <v>0</v>
       </c>
-      <c r="L13" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>17</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="D14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G14" s="2" t="s">
+      <c r="H14" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="H14" s="2" t="s">
-        <v>70</v>
-      </c>
       <c r="I14" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K14" s="2">
         <v>0</v>
       </c>
-      <c r="L14" s="2" t="s">
+    </row>
+    <row r="15" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="3">
+        <v>18</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="3">
-        <v>18</v>
-      </c>
-      <c r="B15" s="3" t="s">
+      <c r="C15" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G15" s="3" t="s">
+      <c r="H15" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>74</v>
-      </c>
       <c r="I15" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>19</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G16" s="2" t="s">
+      <c r="H16" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="H16" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="I16" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K16" s="2">
         <v>0</v>
       </c>
-      <c r="L16" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>15</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G17" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>80</v>
-      </c>
       <c r="H17" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K17" s="3">
         <v>7</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>12</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G18" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G18" s="2" t="s">
+      <c r="H18" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="H18" s="2" t="s">
-        <v>83</v>
-      </c>
       <c r="I18" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K18" s="2">
         <v>7</v>
       </c>
-      <c r="L18" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>20</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="H19" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>85</v>
-      </c>
       <c r="I19" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K19" s="3">
         <v>0</v>
       </c>
-      <c r="L19" s="3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>5</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="D20" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="E20" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>89</v>
-      </c>
       <c r="F20" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K20" s="2">
         <v>12</v>
       </c>
-      <c r="L20" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>21</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="D21" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="E21" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G21" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="G21" s="3" t="s">
+      <c r="H21" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>94</v>
-      </c>
       <c r="I21" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K21" s="3">
         <v>0</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>94</v>
-      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:K1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
